--- a/Taller 3/tablas.xlsx
+++ b/Taller 3/tablas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1655775e314bd799/Maestría IA Aplicada/Semestre 1/Aprendizaje automático III/Talleres/Taller 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{B1D44CD4-F765-41BB-8147-D381176485D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC3F681A-8915-4186-B280-E3030F95059D}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="8_{B1D44CD4-F765-41BB-8147-D381176485D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4EB8658-AA96-4A69-9811-6746ECE1F7D7}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-2475" windowWidth="20730" windowHeight="11040" xr2:uid="{AD1B03CA-9232-4F2D-A5D2-63064345160B}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="185">
   <si>
     <t>Modelo</t>
   </si>
@@ -585,6 +586,51 @@
   </si>
   <si>
     <t>11398.28</t>
+  </si>
+  <si>
+    <t>Mejor RMSE obtenido</t>
+  </si>
+  <si>
+    <t>Parámetro α (alpha)</t>
+  </si>
+  <si>
+    <t>Parámetro β (beta)</t>
+  </si>
+  <si>
+    <t>Parámetro γ (gamma)</t>
+  </si>
+  <si>
+    <t>Tipo de estacionalidad</t>
+  </si>
+  <si>
+    <t>Tamaño de ventana (window_size)</t>
+  </si>
+  <si>
+    <t>Trials ejecutados</t>
+  </si>
+  <si>
+    <t>Trials exitosos</t>
+  </si>
+  <si>
+    <t>0.0092</t>
+  </si>
+  <si>
+    <t>0.5313</t>
+  </si>
+  <si>
+    <t>0.5235</t>
+  </si>
+  <si>
+    <t>add</t>
+  </si>
+  <si>
+    <t>Tipo de tendencia</t>
+  </si>
+  <si>
+    <t>Límite Inferior</t>
+  </si>
+  <si>
+    <t>Límite Superior</t>
   </si>
 </sst>
 </file>
@@ -643,7 +689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -692,6 +738,16 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1031,10 +1087,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{967B6C11-13F9-4C03-BFC2-EFBD0D58981C}">
-  <dimension ref="C9:M114"/>
+  <dimension ref="B9:M141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.81640625" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
     <col min="4" max="4" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.6328125" customWidth="1"/>
@@ -1235,628 +1292,814 @@
         <v>113</v>
       </c>
     </row>
+    <row r="40" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
     <row r="41" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5">
+        <v>43647</v>
+      </c>
+      <c r="D41" s="20">
+        <v>10516.54</v>
+      </c>
+      <c r="E41" s="20">
+        <v>10366.459999999999</v>
+      </c>
+      <c r="F41" s="20">
+        <v>10666.61</v>
+      </c>
+    </row>
+    <row r="42" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C42" s="5">
+        <v>43678</v>
+      </c>
+      <c r="D42" s="20">
+        <v>10618.7</v>
+      </c>
+      <c r="E42" s="20">
+        <v>10468.629999999999</v>
+      </c>
+      <c r="F42" s="20">
+        <v>10768.78</v>
+      </c>
+    </row>
+    <row r="43" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C43" s="5">
+        <v>43709</v>
+      </c>
+      <c r="D43" s="20">
+        <v>10744.68</v>
+      </c>
+      <c r="E43" s="20">
+        <v>10594.6</v>
+      </c>
+      <c r="F43" s="20">
+        <v>10894.75</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C44" s="5">
+        <v>43739</v>
+      </c>
+      <c r="D44" s="20">
+        <v>10774.87</v>
+      </c>
+      <c r="E44" s="20">
+        <v>10624.8</v>
+      </c>
+      <c r="F44" s="20">
+        <v>10924.94</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C45" s="5">
+        <v>43770</v>
+      </c>
+      <c r="D45" s="20">
+        <v>10772.11</v>
+      </c>
+      <c r="E45" s="20">
+        <v>10622.04</v>
+      </c>
+      <c r="F45" s="20">
+        <v>10922.19</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C46" s="5">
+        <v>43800</v>
+      </c>
+      <c r="D46" s="20">
+        <v>10800.85</v>
+      </c>
+      <c r="E46" s="20">
+        <v>10650.77</v>
+      </c>
+      <c r="F46" s="20">
+        <v>10950.92</v>
+      </c>
+    </row>
+    <row r="50" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C50" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C42" s="7">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C51" s="7">
         <v>43647</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D51" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C43" s="7">
-        <v>43678</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F43" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C44" s="7">
-        <v>43709</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C45" s="7">
-        <v>43739</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C46" s="7">
-        <v>43770</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C47" s="7">
-        <v>43800</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="51" spans="3:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="C51" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="52" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C52" s="7">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C53" s="7">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C54" s="7">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C55" s="7">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C56" s="7">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C57" s="7">
-        <v>43800</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="3:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="3:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="C60" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C60" s="7">
-        <v>43647</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>154</v>
+      <c r="E60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C61" s="7">
-        <v>43678</v>
+        <v>43647</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>156</v>
+        <v>46</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C62" s="7">
-        <v>43709</v>
+        <v>43678</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C63" s="7">
-        <v>43739</v>
+        <v>43709</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>161</v>
+        <v>51</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>162</v>
+        <v>52</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C64" s="7">
-        <v>43770</v>
+        <v>43739</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>164</v>
+        <v>54</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C65" s="7">
+        <v>43770</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C66" s="7">
         <v>43800</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D66" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="3:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C69" s="7">
+        <v>43647</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="70" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C70" s="7">
+        <v>43678</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="71" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C71" s="7">
+        <v>43709</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C72" s="7">
+        <v>43739</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="73" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C73" s="7">
+        <v>43770</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="74" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C74" s="7">
+        <v>43800</v>
+      </c>
+      <c r="D74" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E74" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F65" s="8" t="s">
+      <c r="F74" s="8" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C68" s="1" t="s">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C77" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D77" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="C69" s="3" t="s">
+    <row r="78" spans="3:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="C78" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F69" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="29" x14ac:dyDescent="0.35">
-      <c r="C70" s="3" t="s">
+    <row r="79" spans="3:6" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="C79" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="C71" s="3" t="s">
+    <row r="80" spans="3:6" ht="116" x14ac:dyDescent="0.35">
+      <c r="C80" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F71" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="C72" s="3" t="s">
+    <row r="81" spans="3:11" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="C81" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D81" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="C73" s="3" t="s">
+    <row r="82" spans="3:11" ht="116" x14ac:dyDescent="0.35">
+      <c r="C82" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E82" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="82" spans="8:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H82" s="6" t="s">
+    <row r="91" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="H91" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I82" s="6" t="s">
+      <c r="I91" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="J82" s="1" t="s">
+      <c r="J91" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="K82" s="6" t="s">
+      <c r="K91" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="83" spans="8:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H83" s="6" t="s">
+    <row r="92" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="H92" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I83" s="13" t="s">
+      <c r="I92" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="J83" s="4" t="s">
+      <c r="J92" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="K83" s="13" t="s">
+      <c r="K92" s="13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="84" spans="8:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H84" s="6" t="s">
+    <row r="93" spans="3:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="H93" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="I84" s="13" t="s">
+      <c r="I93" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="J84" s="4" t="s">
+      <c r="J93" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="K84" s="13" t="s">
+      <c r="K93" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="85" spans="8:13" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="H85" s="6" t="s">
+    <row r="94" spans="3:11" x14ac:dyDescent="0.35">
+      <c r="H94" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="I85" s="13" t="s">
+      <c r="I94" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="J85" s="4" t="s">
+      <c r="J94" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="K85" s="13" t="s">
+      <c r="K94" s="13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="92" spans="8:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="H92" s="14" t="s">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B99" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C99" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="101" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="H101" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="I92" s="14" t="s">
+      <c r="I101" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="J92" s="14" t="s">
+      <c r="J101" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="K92" s="14" t="s">
+      <c r="K101" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="L92" s="14" t="s">
+      <c r="L101" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="M92" s="14" t="s">
+      <c r="M101" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="8:13" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="H93" s="16" t="s">
+    <row r="102" spans="2:13" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="H102" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="I93" s="15" t="s">
+      <c r="I102" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="J93" s="15" t="s">
+      <c r="J102" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K93" s="15" t="s">
+      <c r="K102" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="L93" s="15" t="s">
+      <c r="L102" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="M93" s="15" t="s">
+      <c r="M102" s="15" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="94" spans="8:13" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="H94" s="16" t="s">
+    <row r="103" spans="2:13" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="H103" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="I94" s="15" t="s">
+      <c r="I103" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="J94" s="15" t="s">
+      <c r="J103" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K94" s="15" t="s">
+      <c r="K103" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="L94" s="15" t="s">
+      <c r="L103" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="M94" s="15" t="s">
+      <c r="M103" s="15" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="95" spans="8:13" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="H95" s="16" t="s">
+    <row r="104" spans="2:13" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="H104" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I95" s="15" t="s">
+      <c r="I104" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="J95" s="15" t="s">
+      <c r="J104" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="K95" s="15" t="s">
+      <c r="K104" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="L95" s="15" t="s">
+      <c r="L104" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="M95" s="15" t="s">
+      <c r="M104" s="15" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="105" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I105" s="9" t="s">
+    <row r="114" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I114" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="J105" s="9" t="s">
+      <c r="J114" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="K105" s="9" t="s">
+      <c r="K114" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="106" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I106" s="10">
+    <row r="115" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I115" s="10">
         <v>2</v>
       </c>
-      <c r="J106" s="10" t="s">
+      <c r="J115" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="K106" s="10" t="s">
+      <c r="K115" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="107" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I107" s="10">
+    <row r="116" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I116" s="10">
         <v>3</v>
       </c>
-      <c r="J107" s="10" t="s">
+      <c r="J116" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="K107" s="10" t="s">
+      <c r="K116" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="108" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I108" s="10">
+    <row r="117" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I117" s="10">
         <v>4</v>
       </c>
-      <c r="J108" s="10" t="s">
+      <c r="J117" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="K108" s="10" t="s">
+      <c r="K117" s="10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="109" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I109" s="10">
+    <row r="118" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I118" s="10">
         <v>5</v>
       </c>
-      <c r="J109" s="10" t="s">
+      <c r="J118" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="K109" s="10" t="s">
+      <c r="K118" s="10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="110" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I110" s="11">
+    <row r="119" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I119" s="11">
         <v>6</v>
       </c>
-      <c r="J110" s="11" t="s">
+      <c r="J119" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K110" s="11" t="s">
+      <c r="K119" s="11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I111" s="10">
+    <row r="120" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I120" s="10">
         <v>7</v>
       </c>
-      <c r="J111" s="12">
+      <c r="J120" s="12">
         <v>-43530</v>
       </c>
-      <c r="K111" s="10" t="s">
+      <c r="K120" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="112" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I112" s="10">
+    <row r="121" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I121" s="10">
         <v>8</v>
       </c>
-      <c r="J112" s="12">
+      <c r="J121" s="12">
         <v>-357405</v>
       </c>
-      <c r="K112" s="10" t="s">
+      <c r="K121" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="113" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I113" s="10">
+    <row r="122" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I122" s="10">
         <v>9</v>
       </c>
-      <c r="J113" s="12">
+      <c r="J122" s="12">
         <v>-370772</v>
       </c>
-      <c r="K113" s="10" t="s">
+      <c r="K122" s="10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="114" spans="9:11" x14ac:dyDescent="0.35">
-      <c r="I114" s="10">
+    <row r="123" spans="9:11" x14ac:dyDescent="0.35">
+      <c r="I123" s="10">
         <v>10</v>
       </c>
-      <c r="J114" s="12">
+      <c r="J123" s="12">
         <v>-381932</v>
       </c>
-      <c r="K114" s="10" t="s">
+      <c r="K123" s="10" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B132" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B133" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C133" s="18">
+        <v>76.568200000000004</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B134" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B135" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B136" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="137" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B137" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B138" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="139" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B139" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C139" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B140" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C140" s="19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B141" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="C141" s="19">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
